--- a/aq_files/0735.xlsx
+++ b/aq_files/0735.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -446,17 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dictionary stores:</t>
+          <t>List is:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A) key-value B) list C) set D) tuple</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) mutable B) immutable C) none D) both</t>
         </is>
       </c>
     </row>
@@ -468,61 +463,51 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Keys must be:</t>
+          <t>Index starts from:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A) immutable B) mutable C) both D) none</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) 0 B) 1 C) -1 D) none</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Values can be:</t>
+          <t>Find running sum of array.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A) any type B) only int C) only str D) none</t>
+          <t>LeetCode-style problem</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dict is ordered?</t>
+          <t>Move zeroes to end.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A) Yes (3.7+) B) No C) maybe D) none</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>LeetCode-style problem</t>
         </is>
       </c>
     </row>
@@ -534,17 +519,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Count frequency of elements.</t>
+          <t>Rotate list by k positions.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -556,7 +536,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Find first non-repeating char.</t>
+          <t>Find maximum subarray sum.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +546,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -578,7 +558,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Group anagrams.</t>
+          <t>Find missing number in list.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +568,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -600,17 +580,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Two sum using dictionary.</t>
+          <t>Check sorted list.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -622,17 +597,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Merge dictionaries.</t>
+          <t>Reverse list in-place.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -644,7 +614,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sort dictionary by value.</t>
+          <t>Find pair with target sum.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +624,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -666,17 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Find key with max value.</t>
+          <t>Remove element from list.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -688,7 +653,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Invert dictionary.</t>
+          <t>Find intersection of sorted lists.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +663,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -710,7 +675,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Check key existence.</t>
+          <t>Find longest increasing subsequence (basic).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +685,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -732,17 +697,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delete key from dictionary.</t>
+          <t>Split list into chunks.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -754,17 +714,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nested dictionary traversal.</t>
+          <t>Flatten nested list.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -776,7 +731,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Word count in sentence.</t>
+          <t>Find first non-repeating element.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +741,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -798,17 +753,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find duplicate keys.</t>
+          <t>Check if list contains duplicates.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -820,17 +770,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combine two dictionaries.</t>
+          <t>Merge sorted lists.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>LeetCode-style problem</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -842,7 +787,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Find intersection of dict keys.</t>
+          <t>Find peak element.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,7 +797,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -864,7 +809,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LRU cache basic logic.</t>
+          <t>Find subarray with given sum.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -874,7 +819,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
